--- a/InputData/trans/AVPC/Annual Vehicle Parking Costs.xlsx
+++ b/InputData/trans/AVPC/Annual Vehicle Parking Costs.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-mexico\InputData\trans\AVPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250317_Trans2/AVPC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C61E0AC-3A82-4945-AF9F-9365208E5A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B44015-09A5-164A-B75F-44BA3FBE624C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{7A96142A-95FE-491D-9737-978D460925CE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23920" windowHeight="20500" activeTab="2" xr2:uid="{7A96142A-95FE-491D-9737-978D460925CE}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="AVPC" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>AVPC Annual Vehicle Parking Costs</t>
   </si>
@@ -47,12 +49,72 @@
     <t>Parking Costs in Major Cities</t>
   </si>
   <si>
+    <t>DEPRISA</t>
+  </si>
+  <si>
+    <t>Mainstream commercial parking lot operator</t>
+  </si>
+  <si>
+    <t>https://deprisa.com.mx/tarifas/</t>
+  </si>
+  <si>
+    <t>Parkmeter system</t>
+  </si>
+  <si>
+    <t>ECOPARQ</t>
+  </si>
+  <si>
+    <t>Parkmeter concession in Mexico City</t>
+  </si>
+  <si>
+    <t>https://www.ecoparq.cdmx.gob.mx/preguntasfrecuentes/preguntas-frecuentes</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
     <t>Conversion Factor</t>
   </si>
   <si>
+    <t>2019 to 2012 USD</t>
+  </si>
+  <si>
+    <t>Simple average</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>yearly cost</t>
+  </si>
+  <si>
+    <t>$/hr</t>
+  </si>
+  <si>
+    <t>of vehicles 5h week</t>
+  </si>
+  <si>
+    <t>$/day</t>
+  </si>
+  <si>
+    <t>of vehicles 5d week</t>
+  </si>
+  <si>
+    <t>monthly</t>
+  </si>
+  <si>
+    <t>of vehicles require it</t>
+  </si>
+  <si>
+    <t>15 min</t>
+  </si>
+  <si>
+    <t>of vehicles 10h week</t>
+  </si>
+  <si>
     <t>2012 USD/year</t>
   </si>
   <si>
@@ -80,85 +142,41 @@
     <t>motorbikes</t>
   </si>
   <si>
-    <t>2019 to 2012 USD</t>
-  </si>
-  <si>
-    <t>DEPRISA</t>
-  </si>
-  <si>
-    <t>Mainstream commercial parking lot operator</t>
-  </si>
-  <si>
-    <t>https://deprisa.com.mx/tarifas/</t>
-  </si>
-  <si>
-    <t>Parkmeter system</t>
-  </si>
-  <si>
-    <t>ECOPARQ</t>
-  </si>
-  <si>
-    <t>Parkmeter concession in Mexico City</t>
-  </si>
-  <si>
-    <t>https://www.ecoparq.cdmx.gob.mx/preguntasfrecuentes/preguntas-frecuentes</t>
-  </si>
-  <si>
-    <t>2019 MXN/yr</t>
-  </si>
-  <si>
-    <t>2019 mxn/usd</t>
-  </si>
-  <si>
-    <t>Simple average</t>
-  </si>
-  <si>
-    <t>unit</t>
-  </si>
-  <si>
-    <t>Assumption</t>
-  </si>
-  <si>
-    <t>yearly cost</t>
-  </si>
-  <si>
-    <t>$/hr</t>
-  </si>
-  <si>
-    <t>of vehicles 5h week</t>
-  </si>
-  <si>
-    <t>$/day</t>
-  </si>
-  <si>
-    <t>of vehicles 5d week</t>
-  </si>
-  <si>
-    <t>monthly</t>
-  </si>
-  <si>
-    <t>of vehicles require it</t>
-  </si>
-  <si>
-    <t>15 min</t>
-  </si>
-  <si>
-    <t>of vehicles 10h week</t>
-  </si>
-  <si>
-    <t>2019 usd / yr</t>
+    <t>2020 to 2012 USD</t>
+  </si>
+  <si>
+    <t>2021 to 2012 USD</t>
+  </si>
+  <si>
+    <t>2022 to 2012 USD</t>
+  </si>
+  <si>
+    <t>MXN/USD FIX</t>
+  </si>
+  <si>
+    <t>2022 mxn/usd</t>
+  </si>
+  <si>
+    <t>Parkmeters</t>
+  </si>
+  <si>
+    <t>2022 usd / yr</t>
+  </si>
+  <si>
+    <t>2022 MXN/yr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+  <numFmts count="4">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,8 +207,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -209,6 +238,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -219,11 +254,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
@@ -242,23 +278,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="6" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="9" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="Comma" xfId="5" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="4" xr:uid="{16EF4BDC-FB9F-4AA5-88EE-16EAB594B4A6}"/>
     <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{98B60151-2F4B-40AD-8582-E6A7B877B213}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{EC07640B-12C8-4008-870A-6D1CF064243E}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -274,9 +311,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -314,7 +351,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -420,7 +457,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -562,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -570,18 +607,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A3C504-1517-4439-8CB6-64CD86FC1AAC}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -589,73 +626,134 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="5"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
-        <v>0.89800000000000002</v>
+        <v>0.89805481563188172</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D19" s="16">
+        <v>2019</v>
+      </c>
+      <c r="E19" s="17">
+        <v>19.261770410958889</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0.88711067149387013</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="16">
+        <v>2020</v>
+      </c>
+      <c r="E20" s="17">
+        <v>21.496090163934426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>0.84730412960844359</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="16">
+        <v>2021</v>
+      </c>
+      <c r="E21" s="17">
+        <v>20.281794246575341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>0.78452102304761584</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="16">
+        <v>2022</v>
+      </c>
+      <c r="E22" s="17">
+        <v>20.124999726027369</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="5"/>
+      <c r="D23" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E23" s="17">
+        <v>17.762000273972614</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{DDB9B43F-5E96-429F-91B6-C7F406976B77}"/>
   </hyperlinks>
@@ -666,518 +764,201 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EEAD45-8CD8-474E-BA40-724705BC176E}">
-  <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="12">
-        <f>SUM(F4:F9)</f>
-        <v>10002.4</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="13">
-        <v>18</v>
-      </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
-        <v>30</v>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
+        <v>32</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="14">
+        <v>17</v>
+      </c>
+      <c r="C4" s="11">
         <f>5*52</f>
         <v>260</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="12">
         <v>0.4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5">
         <f>A4*C4*D4</f>
-        <v>3120</v>
+        <v>3328</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
-        <v>100</v>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
+        <v>120</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="14">
+        <v>19</v>
+      </c>
+      <c r="C5" s="11">
         <f>5*52</f>
         <v>260</v>
       </c>
-      <c r="D5" s="15">
-        <v>0.15</v>
+      <c r="D5" s="12">
+        <v>0.2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F5" s="5">
         <f>A5*C5*D5</f>
-        <v>3900</v>
+        <v>6240</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
-        <v>1000</v>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
+        <v>1200</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="14">
+        <v>21</v>
+      </c>
+      <c r="C6" s="11">
         <v>12</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="12">
         <v>0.2</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F6" s="5">
         <f>A6*C6*D6</f>
-        <v>2400</v>
+        <v>2880</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="16"/>
+      <c r="D7" s="13"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
-      <c r="D8" s="16"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
         <f>2.8</f>
         <v>2.8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="14">
-        <f>10*4*52</f>
-        <v>2080</v>
-      </c>
-      <c r="D9" s="15">
-        <v>0.1</v>
+        <v>23</v>
+      </c>
+      <c r="C9" s="11">
+        <f>4*2*52</f>
+        <v>416</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0.2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F9" s="5">
         <f>A9*C9*D9</f>
-        <v>582.4</v>
+        <v>232.96</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <f>Data!F2/Data!H2</f>
-        <v>555.68888888888887</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D11" s="9"/>
+      <c r="F11" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
+      <c r="F12" s="10">
+        <f>SUM(F4:F9)</f>
+        <v>12680.96</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="18">
+        <f>About!E22</f>
+        <v>20.124999726027369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F13" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F14" s="5">
+        <f>Data!F12/Data!H12</f>
+        <v>630.1098222426258</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1190,38 +971,38 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="3" width="13.42578125" customWidth="1"/>
+    <col min="2" max="3" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="18">
-        <f>Data!A12*About!A19</f>
-        <v>499.00862222222224</v>
+        <v>28</v>
+      </c>
+      <c r="B2" s="15">
+        <f>Data!F14*About!A22</f>
+        <v>494.33440237813613</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
@@ -1230,9 +1011,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1241,9 +1022,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1252,9 +1033,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1263,9 +1044,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -1277,4 +1058,198 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1FAC1C1-42A7-40F7-B68E-BCD3B8B14A78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5430920-531B-4DCD-8F21-6DA09BFBCB77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86D33DB-0ADE-4496-A16A-B2BD143333C8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>